--- a/Docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/Docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73F73E1-2A79-4223-A982-5FF8B7D6E016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-1584" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="1" r:id="rId1"/>
@@ -692,24 +692,6 @@
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -745,28 +727,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -781,13 +745,49 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1058,293 +1058,293 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="7"/>
-    <col min="2" max="2" width="12.28515625" style="7" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="7" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="7"/>
-    <col min="9" max="9" width="21" style="7" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="7" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="7"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="1"/>
+    <col min="9" max="9" width="21" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="30">
+      <c r="J3" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="H4" s="30" t="s">
+      <c r="E4" s="41"/>
+      <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="H5" s="30" t="s">
+      <c r="E5" s="42"/>
+      <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="12"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="10">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="10">
+      <c r="B11" s="4">
         <f t="shared" ref="B11:B25" si="0">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="10">
+      <c r="B12" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="B13" s="10">
+      <c r="B13" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="B14" s="10">
+      <c r="B14" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="10">
+      <c r="B15" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="10">
+      <c r="B16" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="10">
+      <c r="B17" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="10">
+      <c r="B18" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="19"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="10">
+      <c r="B19" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="19"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="10">
+      <c r="B20" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="19"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="10">
+      <c r="B21" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="19"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="10">
+      <c r="B22" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="19"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="10">
+      <c r="B23" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="19"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="10">
+      <c r="B24" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="19"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="10">
+      <c r="B25" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="19"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="27" spans="2:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22" t="s">
+      <c r="D27" s="15"/>
+      <c r="E27" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1370,219 +1370,219 @@
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="7"/>
-    <col min="2" max="2" width="12.28515625" style="7" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="7" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="7"/>
-    <col min="9" max="9" width="22.140625" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="7"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="1"/>
+    <col min="9" max="9" width="22.140625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="30">
+      <c r="J3" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="H4" s="30" t="s">
+      <c r="E4" s="43"/>
+      <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="H5" s="30" t="s">
+      <c r="E5" s="44"/>
+      <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="12"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="10">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="B11" s="10">
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
         <f t="shared" ref="B11:B26" si="0">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="10">
+      <c r="B12" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="10">
+      <c r="B13" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B14" s="10">
+      <c r="B14" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="10">
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="10">
+      <c r="B16" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="12" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="10">
+      <c r="B17" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1591,92 +1591,92 @@
       <c r="E17"/>
     </row>
     <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="10">
+      <c r="B18" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="10">
+      <c r="B19" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="10">
+      <c r="B20" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="18"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="10">
+      <c r="B21" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="18"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="10">
+      <c r="B22" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="18"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="10">
+      <c r="B23" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="18"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="10">
+      <c r="B24" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="18"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="10">
+      <c r="B25" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="18"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="10">
+      <c r="B26" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="18"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="16"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1700,369 +1700,369 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="26"/>
-    <col min="2" max="2" width="12.28515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="18" style="27" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="26" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="26"/>
-    <col min="9" max="9" width="26.7109375" style="26" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="26"/>
+    <col min="1" max="1" width="8.85546875" style="20"/>
+    <col min="2" max="2" width="12.28515625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="18" style="21" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="20" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="20"/>
+    <col min="9" max="9" width="26.7109375" style="20" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="30">
+      <c r="J3" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="H4" s="30" t="s">
+      <c r="E4" s="37"/>
+      <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="H5" s="30" t="s">
+      <c r="E5" s="46"/>
+      <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="35"/>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="26" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="30">
+      <c r="B10" s="22">
         <v>1</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="29" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="30">
+      <c r="B11" s="22">
         <v>2</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="29" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="30">
+      <c r="B12" s="22">
         <v>3</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="29" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="B13" s="30">
+      <c r="B13" s="22">
         <v>4</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="29" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="B14" s="30">
+      <c r="B14" s="22">
         <v>5</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="29" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="30">
+      <c r="B15" s="22">
         <f t="shared" ref="B15:B30" si="0">B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="29" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="30">
+      <c r="B16" s="22">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="29" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B17" s="30">
+      <c r="B17" s="22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="B18" s="30">
+      <c r="B18" s="22">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="29" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="30">
+      <c r="B19" s="22">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B20" s="30">
+    <row r="20" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B20" s="22">
         <f>B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="29" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="30">
+      <c r="B21" s="22">
         <v>12</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
     </row>
     <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="30">
+      <c r="B22" s="22">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
     </row>
     <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="30">
+      <c r="B23" s="22">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
     </row>
     <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="30">
+      <c r="B24" s="22">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
     </row>
     <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="30">
+      <c r="B25" s="22">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
     </row>
     <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="30">
+      <c r="B26" s="22">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
     </row>
     <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="30">
+      <c r="B27" s="22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="40"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="28"/>
     </row>
     <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="30">
+      <c r="B28" s="22">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
     </row>
     <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="30">
+      <c r="B29" s="22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
     </row>
     <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="30">
+      <c r="B30" s="22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
     </row>
     <row r="32" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="43"/>
-      <c r="E32" s="40" t="s">
+      <c r="D32" s="31"/>
+      <c r="E32" s="28" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
     <mergeCell ref="D6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2088,413 +2088,413 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="26"/>
-    <col min="2" max="2" width="12.28515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="18" style="26" customWidth="1"/>
-    <col min="5" max="5" width="45.5703125" style="26" customWidth="1"/>
-    <col min="6" max="6" width="47.28515625" style="26" customWidth="1"/>
-    <col min="7" max="8" width="8.85546875" style="26"/>
-    <col min="9" max="9" width="26.7109375" style="26" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="26"/>
+    <col min="1" max="1" width="8.85546875" style="20"/>
+    <col min="2" max="2" width="12.28515625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="18" style="20" customWidth="1"/>
+    <col min="5" max="5" width="45.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="47.28515625" style="20" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" style="20"/>
+    <col min="9" max="9" width="26.7109375" style="20" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="30">
+      <c r="J3" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="H4" s="30" t="s">
+      <c r="E4" s="37"/>
+      <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="22">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="H5" s="30" t="s">
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="35"/>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="B10" s="30">
+      <c r="B10" s="22">
         <v>1</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="29" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="30">
+      <c r="B11" s="22">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="29" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="B12" s="30">
+      <c r="B12" s="22">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="29" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="105" x14ac:dyDescent="0.25">
-      <c r="B13" s="30">
+      <c r="B13" s="22">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="29" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="B14" s="30">
+      <c r="B14" s="22">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="29" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="30">
+      <c r="B15" s="22">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="29" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="30">
+      <c r="B16" s="22">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="29" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="B17" s="30">
+      <c r="B17" s="22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="29" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B18" s="30">
+      <c r="B18" s="22">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="29" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="B19" s="30">
+      <c r="B19" s="22">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="29" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="B20" s="30">
+      <c r="B20" s="22">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="29" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="30">
+      <c r="B21" s="22">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
     </row>
     <row r="22" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="30">
+      <c r="B22" s="22">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
     </row>
     <row r="23" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="30">
+      <c r="B23" s="22">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
     </row>
     <row r="24" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="30">
+      <c r="B24" s="22">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
     </row>
     <row r="25" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="30">
+      <c r="B25" s="22">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
     </row>
     <row r="26" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="30">
+      <c r="B26" s="22">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
     </row>
     <row r="27" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="30">
+      <c r="B27" s="22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="30">
+      <c r="B28" s="22">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
     </row>
     <row r="29" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="30">
+      <c r="B29" s="22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
     </row>
     <row r="30" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="30">
+      <c r="B30" s="22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
     </row>
     <row r="32" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="46"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/Docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Facultate\VVSS\Proiect_VVSS\Docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73F73E1-2A79-4223-A982-5FF8B7D6E016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149E3838-CF02-4F4E-B6D2-EABCB86EB2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-1584" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="144">
   <si>
     <t>do not print this form</t>
   </si>
@@ -472,18 +472,64 @@
   <si>
     <t>SonarQube</t>
   </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>CsvExporter.java</t>
+  </si>
+  <si>
+    <t>Nu se verifica daca lista este goala inainte sa se apeleze get(0)</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FileStockRepository.java, liniile 22–24</t>
+  </si>
+  <si>
+    <t>cantitatea si stocMinim sunt parsate ca int, dar ele trebuie sa fie de tip double</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>RetetaValidator liniile 23-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesajul de eroare nu este formatat corect (nu are spatii sau endline) </t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>nu s-a gasit</t>
+  </si>
+  <si>
+    <t>05.03.2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -690,104 +736,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,19 +1120,19 @@
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
         <v>3</v>
@@ -1109,10 +1156,10 @@
       <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="41"/>
+      <c r="E4" s="38"/>
       <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
@@ -1127,10 +1174,10 @@
       <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="42"/>
+      <c r="E5" s="39"/>
       <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
@@ -1142,15 +1189,19 @@
       <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
+      <c r="D6" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
+      <c r="D7" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="33"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -1384,19 +1435,19 @@
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
         <v>3</v>
@@ -1420,10 +1471,10 @@
       <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="43"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
@@ -1438,10 +1489,10 @@
       <c r="C5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="44"/>
+      <c r="E5" s="37"/>
       <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
@@ -1453,15 +1504,19 @@
       <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
+      <c r="D6" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
+      <c r="D7" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="33"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -1715,19 +1770,19 @@
       <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
         <v>3</v>
@@ -1751,10 +1806,10 @@
       <c r="C4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="42"/>
       <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
@@ -1769,10 +1824,10 @@
       <c r="C5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="46"/>
+      <c r="E5" s="44"/>
       <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
@@ -1784,15 +1839,19 @@
       <c r="C6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
+      <c r="D6" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="C7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
+      <c r="D7" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
@@ -1809,7 +1868,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="22">
+      <c r="B10" s="47">
         <v>1</v>
       </c>
       <c r="C10" s="28" t="s">
@@ -1823,7 +1882,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="22">
+      <c r="B11" s="47">
         <v>2</v>
       </c>
       <c r="C11" s="28" t="s">
@@ -1837,7 +1896,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="22">
+      <c r="B12" s="47">
         <v>3</v>
       </c>
       <c r="C12" s="28" t="s">
@@ -1851,7 +1910,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="B13" s="22">
+      <c r="B13" s="47">
         <v>4</v>
       </c>
       <c r="C13" s="28" t="s">
@@ -1865,7 +1924,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="B14" s="22">
+      <c r="B14" s="47">
         <v>5</v>
       </c>
       <c r="C14" s="28" t="s">
@@ -1879,7 +1938,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="22">
+      <c r="B15" s="47">
         <f t="shared" ref="B15:B30" si="0">B14+1</f>
         <v>6</v>
       </c>
@@ -1894,7 +1953,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="22">
+      <c r="B16" s="47">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1909,7 +1968,7 @@
       </c>
     </row>
     <row r="17" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B17" s="22">
+      <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1924,7 +1983,7 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="B18" s="22">
+      <c r="B18" s="47">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1939,7 +1998,7 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="22">
+      <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1954,7 +2013,7 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B20" s="22">
+      <c r="B20" s="47">
         <f>B19+1</f>
         <v>11</v>
       </c>
@@ -1968,43 +2027,67 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="22">
+    <row r="21" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B21" s="47">
         <v>12</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-    </row>
-    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="22">
+      <c r="C21" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B22" s="47">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-    </row>
-    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="22">
+      <c r="C22" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="47">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+      <c r="C23" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="22">
+      <c r="B24" s="47">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
+      <c r="C24" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="22">
+      <c r="B25" s="47">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -2013,7 +2096,7 @@
       <c r="E25" s="29"/>
     </row>
     <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="22">
+      <c r="B26" s="47">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -2022,7 +2105,7 @@
       <c r="E26" s="29"/>
     </row>
     <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="22">
+      <c r="B27" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -2031,7 +2114,7 @@
       <c r="E27" s="28"/>
     </row>
     <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="22">
+      <c r="B28" s="47">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -2040,7 +2123,7 @@
       <c r="E28" s="29"/>
     </row>
     <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="22">
+      <c r="B29" s="47">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -2049,7 +2132,7 @@
       <c r="E29" s="29"/>
     </row>
     <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="22">
+      <c r="B30" s="47">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -2104,19 +2187,19 @@
       <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22" t="s">
         <v>3</v>
@@ -2140,10 +2223,10 @@
       <c r="C4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="42"/>
       <c r="H4" s="22" t="s">
         <v>8</v>
       </c>
@@ -2158,8 +2241,10 @@
       <c r="C5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="D5" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="40"/>
       <c r="H5" s="22" t="s">
         <v>11</v>
       </c>
@@ -2171,8 +2256,10 @@
       <c r="C6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
+      <c r="D6" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
@@ -2489,11 +2576,11 @@
       <c r="F30" s="29"/>
     </row>
     <row r="32" spans="2:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
       <c r="F32" s="32"/>
     </row>
   </sheetData>
